--- a/exports/trend_1d/NATIONALUM_full_report.xlsx
+++ b/exports/trend_1d/NATIONALUM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q93"/>
+  <dimension ref="A1:U93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42081</v>
+        <v>42082</v>
       </c>
       <c r="H2" t="n">
-        <v>45.19</v>
+        <v>44.21</v>
       </c>
       <c r="I2" t="n">
         <v>45.14459610350168</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.31</v>
+        <v>-4.43</v>
       </c>
       <c r="L2" t="n">
         <v>5.71</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>10.54</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42093</v>
+        <v>42094</v>
       </c>
       <c r="H3" t="n">
-        <v>43.67</v>
+        <v>45.68</v>
       </c>
       <c r="I3" t="n">
         <v>45.07659407359866</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>1.22</v>
+        <v>-3.33</v>
       </c>
       <c r="L3" t="n">
-        <v>3.21</v>
+        <v>4.09</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="N3" t="n">
         <v>5.08</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>10.22</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42157</v>
+        <v>42158</v>
       </c>
       <c r="H4" t="n">
-        <v>47.14</v>
+        <v>44.75</v>
       </c>
       <c r="I4" t="n">
         <v>45.06485526440373</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>-2.04</v>
       </c>
       <c r="L4" t="n">
-        <v>3.02</v>
+        <v>5.47</v>
       </c>
       <c r="M4" t="n">
         <v>0.11</v>
       </c>
       <c r="N4" t="n">
-        <v>3.14</v>
+        <v>5.07</v>
       </c>
       <c r="O4" t="n">
         <v>4.6</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.16</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42220</v>
+        <v>42221</v>
       </c>
       <c r="H5" t="n">
-        <v>36.37</v>
+        <v>37.89</v>
       </c>
       <c r="I5" t="n">
         <v>37.80602114589695</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K5" t="n">
-        <v>18.73</v>
+        <v>15.33</v>
       </c>
       <c r="L5" t="n">
         <v>6.32</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>10.24</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42228</v>
+        <v>42229</v>
       </c>
       <c r="H6" t="n">
-        <v>35.74</v>
+        <v>32.26</v>
       </c>
       <c r="I6" t="n">
         <v>34.41276058464113</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.67</v>
+        <v>-14.86</v>
       </c>
       <c r="L6" t="n">
-        <v>6.6</v>
+        <v>15.28</v>
       </c>
       <c r="M6" t="n">
-        <v>0.62</v>
+        <v>1.65</v>
       </c>
       <c r="N6" t="n">
-        <v>4.18</v>
+        <v>9.74</v>
       </c>
       <c r="O6" t="n">
         <v>4.18</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>20.05</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42255</v>
+        <v>42256</v>
       </c>
       <c r="H7" t="n">
-        <v>33.08</v>
+        <v>33.82</v>
       </c>
       <c r="I7" t="n">
         <v>33.09341262722967</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.54</v>
+        <v>-4.84</v>
       </c>
       <c r="L7" t="n">
         <v>9.109999999999999</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>13.49</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42317</v>
+        <v>42318</v>
       </c>
       <c r="H8" t="n">
-        <v>36.67</v>
+        <v>35.35</v>
       </c>
       <c r="I8" t="n">
         <v>36.16186399487361</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K8" t="n">
-        <v>8.43</v>
+        <v>4.52</v>
       </c>
       <c r="L8" t="n">
         <v>4.76</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>11.73</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42335</v>
+        <v>42338</v>
       </c>
       <c r="H9" t="n">
-        <v>38.82</v>
+        <v>39.65</v>
       </c>
       <c r="I9" t="n">
         <v>39.40886649005974</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.82</v>
+        <v>-12.16</v>
       </c>
       <c r="L9" t="n">
-        <v>12.16</v>
+        <v>12.73</v>
       </c>
       <c r="M9" t="n">
         <v>3.43</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>11.5</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42375</v>
+        <v>42376</v>
       </c>
       <c r="H10" t="n">
-        <v>37.79</v>
+        <v>36.42</v>
       </c>
       <c r="I10" t="n">
         <v>37.40497563748504</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.69</v>
+        <v>-8.15</v>
       </c>
       <c r="L10" t="n">
-        <v>6.68</v>
+        <v>9</v>
       </c>
       <c r="M10" t="n">
-        <v>0.91</v>
+        <v>1.53</v>
       </c>
       <c r="N10" t="n">
         <v>6.97</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>12.82</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42431</v>
+        <v>42432</v>
       </c>
       <c r="H11" t="n">
-        <v>32.9</v>
+        <v>35.88</v>
       </c>
       <c r="I11" t="n">
         <v>35.09265546297497</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K11" t="n">
-        <v>9.67</v>
+        <v>1.48</v>
       </c>
       <c r="L11" t="n">
         <v>11.04</v>
@@ -1068,7 +1199,7 @@
         <v>2.35</v>
       </c>
       <c r="N11" t="n">
-        <v>4.54</v>
+        <v>9.06</v>
       </c>
       <c r="O11" t="n">
         <v>-3.63</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>17.39</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42503</v>
+        <v>42506</v>
       </c>
       <c r="H12" t="n">
-        <v>41.81</v>
+        <v>40.78</v>
       </c>
       <c r="I12" t="n">
         <v>40.92509942360724</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K12" t="n">
-        <v>16.53</v>
+        <v>13.66</v>
       </c>
       <c r="L12" t="n">
         <v>10.09</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>15.1</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42556</v>
+        <v>42558</v>
       </c>
       <c r="H13" t="n">
-        <v>42.93</v>
+        <v>43.33</v>
       </c>
       <c r="I13" t="n">
         <v>43.07873370674658</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.27</v>
+        <v>-6.25</v>
       </c>
       <c r="L13" t="n">
-        <v>6.6</v>
+        <v>7.09</v>
       </c>
       <c r="M13" t="n">
         <v>4.94</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.86</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42628</v>
+        <v>42629</v>
       </c>
       <c r="H14" t="n">
-        <v>45.09</v>
+        <v>43.57</v>
       </c>
       <c r="I14" t="n">
         <v>44.32771115632531</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K14" t="n">
-        <v>4.06</v>
+        <v>0.55</v>
       </c>
       <c r="L14" t="n">
         <v>2.38</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>14.94</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42650</v>
+        <v>42653</v>
       </c>
       <c r="H15" t="n">
-        <v>48.07</v>
+        <v>51.31</v>
       </c>
       <c r="I15" t="n">
         <v>48.71682073952951</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K15" t="n">
-        <v>-10.33</v>
+        <v>-17.76</v>
       </c>
       <c r="L15" t="n">
-        <v>11.25</v>
+        <v>18.43</v>
       </c>
       <c r="M15" t="n">
-        <v>1.18</v>
+        <v>5.91</v>
       </c>
       <c r="N15" t="n">
-        <v>2.71</v>
+        <v>6.74</v>
       </c>
       <c r="O15" t="n">
         <v>-3.37</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>12.37</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42689</v>
+        <v>42690</v>
       </c>
       <c r="H16" t="n">
-        <v>48.07</v>
+        <v>47.39</v>
       </c>
       <c r="I16" t="n">
         <v>47.97946737575215</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.31</v>
+        <v>-7.64</v>
       </c>
       <c r="L16" t="n">
         <v>14.13</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>18.15</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42699</v>
+        <v>42702</v>
       </c>
       <c r="H17" t="n">
-        <v>55.81</v>
+        <v>56.25</v>
       </c>
       <c r="I17" t="n">
         <v>55.8579869593415</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K17" t="n">
-        <v>-17.77</v>
+        <v>-18.7</v>
       </c>
       <c r="L17" t="n">
-        <v>19.84</v>
+        <v>20.76</v>
       </c>
       <c r="M17" t="n">
         <v>3.41</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>14.78</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42725</v>
+        <v>42726</v>
       </c>
       <c r="H18" t="n">
-        <v>58.21</v>
+        <v>55.86</v>
       </c>
       <c r="I18" t="n">
         <v>57.39172203126353</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K18" t="n">
-        <v>3.48</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L18" t="n">
         <v>6.61</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>20.89</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42734</v>
+        <v>42737</v>
       </c>
       <c r="H19" t="n">
-        <v>63.94</v>
+        <v>65.45</v>
       </c>
       <c r="I19" t="n">
         <v>65.22710365590994</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K19" t="n">
-        <v>-14.46</v>
+        <v>-17.17</v>
       </c>
       <c r="L19" t="n">
-        <v>15.59</v>
+        <v>18.05</v>
       </c>
       <c r="M19" t="n">
         <v>1.34</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>18.3</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42774</v>
+        <v>42775</v>
       </c>
       <c r="H20" t="n">
-        <v>70.01000000000001</v>
+        <v>66.63</v>
       </c>
       <c r="I20" t="n">
         <v>67.72559960608949</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K20" t="n">
-        <v>6.97</v>
+        <v>1.8</v>
       </c>
       <c r="L20" t="n">
         <v>4.94</v>
@@ -1581,7 +1820,7 @@
         <v>0.82</v>
       </c>
       <c r="N20" t="n">
-        <v>4.54</v>
+        <v>4.83</v>
       </c>
       <c r="O20" t="n">
         <v>2.36</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>18.08</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42795</v>
+        <v>42796</v>
       </c>
       <c r="H21" t="n">
-        <v>70.06</v>
+        <v>73.73</v>
       </c>
       <c r="I21" t="n">
         <v>72.69237727529365</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.15</v>
+        <v>-10.66</v>
       </c>
       <c r="L21" t="n">
-        <v>6.47</v>
+        <v>13.66</v>
       </c>
       <c r="M21" t="n">
         <v>2.11</v>
       </c>
       <c r="N21" t="n">
-        <v>3.78</v>
+        <v>5.24</v>
       </c>
       <c r="O21" t="n">
         <v>-4.83</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>13.14</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>42843</v>
+        <v>42844</v>
       </c>
       <c r="H22" t="n">
-        <v>71.92</v>
+        <v>66.33</v>
       </c>
       <c r="I22" t="n">
         <v>67.88765652209659</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.45</v>
+        <v>-10.04</v>
       </c>
       <c r="L22" t="n">
         <v>11.03</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="N22" t="n">
-        <v>5.32</v>
+        <v>7.77</v>
       </c>
       <c r="O22" t="n">
         <v>5.24</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>14.03</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>42919</v>
+        <v>42920</v>
       </c>
       <c r="H23" t="n">
-        <v>63.4</v>
+        <v>65.89</v>
       </c>
       <c r="I23" t="n">
         <v>65.27283329744004</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K23" t="n">
-        <v>4.42</v>
+        <v>0.66</v>
       </c>
       <c r="L23" t="n">
         <v>5.4</v>
@@ -1752,7 +2027,7 @@
         <v>1.89</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>3.93</v>
       </c>
       <c r="O23" t="n">
         <v>-7.77</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>10.18</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>42957</v>
+        <v>42958</v>
       </c>
       <c r="H24" t="n">
-        <v>63.64</v>
+        <v>61.19</v>
       </c>
       <c r="I24" t="n">
         <v>63.15742272885168</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.41</v>
+        <v>-7.13</v>
       </c>
       <c r="L24" t="n">
-        <v>5.78</v>
+        <v>7.65</v>
       </c>
       <c r="M24" t="n">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="N24" t="n">
         <v>7.67</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>17.49</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>42978</v>
+        <v>42979</v>
       </c>
       <c r="H25" t="n">
-        <v>70.73999999999999</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="I25" t="n">
         <v>71.89157094493169</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K25" t="n">
-        <v>-15.61</v>
+        <v>-19.77</v>
       </c>
       <c r="L25" t="n">
-        <v>16.65</v>
+        <v>20.33</v>
       </c>
       <c r="M25" t="n">
-        <v>1.05</v>
+        <v>1.67</v>
       </c>
       <c r="N25" t="n">
         <v>5.85</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>12.08</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43053</v>
+        <v>43054</v>
       </c>
       <c r="H26" t="n">
-        <v>83.31999999999999</v>
+        <v>78.48</v>
       </c>
       <c r="I26" t="n">
         <v>83.24963185516287</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K26" t="n">
-        <v>13.69</v>
+        <v>7.08</v>
       </c>
       <c r="L26" t="n">
         <v>5.08</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>18.22</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43096</v>
+        <v>43097</v>
       </c>
       <c r="H27" t="n">
-        <v>79.65000000000001</v>
+        <v>84.55</v>
       </c>
       <c r="I27" t="n">
         <v>82.22132661496067</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.49</v>
+        <v>-7.73</v>
       </c>
       <c r="L27" t="n">
-        <v>7.79</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="M27" t="n">
         <v>2.41</v>
       </c>
       <c r="N27" t="n">
-        <v>4.48</v>
+        <v>6.15</v>
       </c>
       <c r="O27" t="n">
         <v>-5.81</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>12.87</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43115</v>
+        <v>43116</v>
       </c>
       <c r="H28" t="n">
-        <v>84.55</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="I28" t="n">
         <v>78.16305453912734</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L28" t="n">
-        <v>4.81</v>
+        <v>8.52</v>
       </c>
       <c r="M28" t="n">
         <v>0.4</v>
       </c>
       <c r="N28" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="O28" t="n">
         <v>6.15</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>17.02</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43194</v>
+        <v>43195</v>
       </c>
       <c r="H29" t="n">
-        <v>68.64</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="I29" t="n">
         <v>69.98418402013094</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K29" t="n">
-        <v>11.76</v>
+        <v>9.32</v>
       </c>
       <c r="L29" t="n">
         <v>9.69</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.66</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43231</v>
+        <v>43234</v>
       </c>
       <c r="H30" t="n">
-        <v>76.47</v>
+        <v>73.73</v>
       </c>
       <c r="I30" t="n">
         <v>74.71361567189128</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K30" t="n">
-        <v>8.41</v>
+        <v>4.52</v>
       </c>
       <c r="L30" t="n">
         <v>3.33</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>13.67</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43315</v>
+        <v>43318</v>
       </c>
       <c r="H31" t="n">
-        <v>64.33</v>
+        <v>65.11</v>
       </c>
       <c r="I31" t="n">
         <v>64.67415014449156</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K31" t="n">
-        <v>12.75</v>
+        <v>11.69</v>
       </c>
       <c r="L31" t="n">
         <v>3.92</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>11.37</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H32" t="n">
-        <v>67.26000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="I32" t="n">
         <v>66.24891112200521</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K32" t="n">
-        <v>3.3</v>
+        <v>-1.12</v>
       </c>
       <c r="L32" t="n">
-        <v>2.41</v>
+        <v>6.77</v>
       </c>
       <c r="M32" t="n">
         <v>0.6899999999999999</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>15.38</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43406</v>
+        <v>43409</v>
       </c>
       <c r="H33" t="n">
-        <v>67.84999999999999</v>
+        <v>69.42</v>
       </c>
       <c r="I33" t="n">
         <v>68.95728919788441</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.39</v>
+        <v>-7.83</v>
       </c>
       <c r="L33" t="n">
         <v>9.720000000000001</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>13.06</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43441</v>
+        <v>43444</v>
       </c>
       <c r="H34" t="n">
-        <v>61.98</v>
+        <v>60.41</v>
       </c>
       <c r="I34" t="n">
         <v>61.17446885570472</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K34" t="n">
-        <v>-10.72</v>
+        <v>-12.98</v>
       </c>
       <c r="L34" t="n">
-        <v>12.13</v>
+        <v>15.37</v>
       </c>
       <c r="M34" t="n">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="N34" t="n">
         <v>4.56</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>10.22</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H35" t="n">
-        <v>52.53</v>
+        <v>54.93</v>
       </c>
       <c r="I35" t="n">
         <v>53.60350910527117</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K35" t="n">
-        <v>13.04</v>
+        <v>9.07</v>
       </c>
       <c r="L35" t="n">
         <v>6.97</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>14.46</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43588</v>
+        <v>43591</v>
       </c>
       <c r="H36" t="n">
-        <v>51.06</v>
+        <v>49.89</v>
       </c>
       <c r="I36" t="n">
         <v>50.37279963493876</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K36" t="n">
-        <v>-7.05</v>
+        <v>-9.18</v>
       </c>
       <c r="L36" t="n">
-        <v>8.92</v>
+        <v>9.81</v>
       </c>
       <c r="M36" t="n">
         <v>8.09</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43713</v>
+        <v>43714</v>
       </c>
       <c r="H37" t="n">
-        <v>41.22</v>
+        <v>42.35</v>
       </c>
       <c r="I37" t="n">
         <v>41.99142608198449</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K37" t="n">
-        <v>17.38</v>
+        <v>15.11</v>
       </c>
       <c r="L37" t="n">
         <v>1.86</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>13.31</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43748</v>
+        <v>43749</v>
       </c>
       <c r="H38" t="n">
-        <v>41.27</v>
+        <v>40.19</v>
       </c>
       <c r="I38" t="n">
         <v>40.9630218163034</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.55</v>
+        <v>-5.1</v>
       </c>
       <c r="L38" t="n">
-        <v>4.27</v>
+        <v>6.26</v>
       </c>
       <c r="M38" t="n">
         <v>1.9</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>19.2</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43770</v>
+        <v>43773</v>
       </c>
       <c r="H39" t="n">
-        <v>45.04</v>
+        <v>45.82</v>
       </c>
       <c r="I39" t="n">
         <v>45.37192637297524</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>-12.07</v>
+        <v>-14.01</v>
       </c>
       <c r="L39" t="n">
-        <v>13.04</v>
+        <v>16.32</v>
       </c>
       <c r="M39" t="n">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="N39" t="n">
         <v>8.390000000000001</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>11.12</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43787</v>
+        <v>43788</v>
       </c>
       <c r="H40" t="n">
-        <v>41.47</v>
+        <v>41.17</v>
       </c>
       <c r="I40" t="n">
         <v>41.17667438474366</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K40" t="n">
-        <v>-9.49</v>
+        <v>-10.15</v>
       </c>
       <c r="L40" t="n">
         <v>12.18</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>11.19</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>43831</v>
+        <v>43832</v>
       </c>
       <c r="H41" t="n">
-        <v>42.3</v>
+        <v>44.99</v>
       </c>
       <c r="I41" t="n">
         <v>44.59504476293384</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.74</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>8.210000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="M41" t="n">
         <v>0.97</v>
       </c>
       <c r="N41" t="n">
-        <v>4.02</v>
+        <v>6.36</v>
       </c>
       <c r="O41" t="n">
         <v>-0.72</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>12.23</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>43860</v>
+        <v>43861</v>
       </c>
       <c r="H42" t="n">
-        <v>42.98</v>
+        <v>41.66</v>
       </c>
       <c r="I42" t="n">
         <v>42.48687042664813</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.47</v>
+        <v>-7.4</v>
       </c>
       <c r="L42" t="n">
-        <v>6.2</v>
+        <v>7.94</v>
       </c>
       <c r="M42" t="n">
         <v>1.43</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,25 +3386,25 @@
         <v>11.51</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>43938</v>
+        <v>43941</v>
       </c>
       <c r="H43" t="n">
-        <v>31.28</v>
+        <v>33.39</v>
       </c>
       <c r="I43" t="n">
         <v>33.17535385696856</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K43" t="n">
-        <v>24.92</v>
+        <v>19.85</v>
       </c>
       <c r="L43" t="n">
         <v>6.34</v>
       </c>
       <c r="M43" t="n">
-        <v>2.54</v>
+        <v>3.29</v>
       </c>
       <c r="N43" t="n">
         <v>13.31</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>19.17</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>43958</v>
+        <v>43959</v>
       </c>
       <c r="H44" t="n">
-        <v>28.25</v>
+        <v>27.76</v>
       </c>
       <c r="I44" t="n">
         <v>27.92096469841057</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K44" t="n">
-        <v>-15.39</v>
+        <v>-16.86</v>
       </c>
       <c r="L44" t="n">
-        <v>16.14</v>
+        <v>17.76</v>
       </c>
       <c r="M44" t="n">
         <v>3.38</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>18.32</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>43986</v>
+        <v>43987</v>
       </c>
       <c r="H45" t="n">
-        <v>29.81</v>
+        <v>32.11</v>
       </c>
       <c r="I45" t="n">
         <v>30.77636049538443</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.38</v>
+        <v>-15.67</v>
       </c>
       <c r="L45" t="n">
-        <v>12.32</v>
+        <v>16.93</v>
       </c>
       <c r="M45" t="n">
         <v>5.54</v>
       </c>
       <c r="N45" t="n">
-        <v>5.06</v>
+        <v>7.72</v>
       </c>
       <c r="O45" t="n">
         <v>-1.73</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>16.5</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44081</v>
+        <v>44082</v>
       </c>
       <c r="H46" t="n">
-        <v>35.44</v>
+        <v>33.98</v>
       </c>
       <c r="I46" t="n">
         <v>34.16744338292948</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K46" t="n">
-        <v>10.37</v>
+        <v>5.82</v>
       </c>
       <c r="L46" t="n">
         <v>10.65</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>15.02</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44141</v>
+        <v>44144</v>
       </c>
       <c r="H47" t="n">
-        <v>31.97</v>
+        <v>32.51</v>
       </c>
       <c r="I47" t="n">
         <v>32.07413394606298</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K47" t="n">
-        <v>5.92</v>
+        <v>4.33</v>
       </c>
       <c r="L47" t="n">
         <v>5.03</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>10.42</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44278</v>
+        <v>44279</v>
       </c>
       <c r="H48" t="n">
-        <v>53.8</v>
+        <v>52.19</v>
       </c>
       <c r="I48" t="n">
         <v>52.65759271738254</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K48" t="n">
-        <v>65.48999999999999</v>
+        <v>60.54</v>
       </c>
       <c r="L48" t="n">
         <v>2.86</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>15.37</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44293</v>
+        <v>44294</v>
       </c>
       <c r="H49" t="n">
-        <v>57.91</v>
+        <v>59.09</v>
       </c>
       <c r="I49" t="n">
         <v>58.65985192412701</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K49" t="n">
-        <v>-10.96</v>
+        <v>-13.22</v>
       </c>
       <c r="L49" t="n">
-        <v>13.97</v>
+        <v>15.85</v>
       </c>
       <c r="M49" t="n">
         <v>1.65</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>12.94</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44364</v>
+        <v>44365</v>
       </c>
       <c r="H50" t="n">
-        <v>67.22</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="I50" t="n">
         <v>66.37823115138156</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K50" t="n">
-        <v>13.76</v>
+        <v>12.1</v>
       </c>
       <c r="L50" t="n">
         <v>12.59</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>12.62</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44372</v>
+        <v>44375</v>
       </c>
       <c r="H51" t="n">
-        <v>71.92</v>
+        <v>78.38</v>
       </c>
       <c r="I51" t="n">
         <v>74.60167001248109</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K51" t="n">
-        <v>-8.57</v>
+        <v>-18.33</v>
       </c>
       <c r="L51" t="n">
-        <v>9.68</v>
+        <v>24.61</v>
       </c>
       <c r="M51" t="n">
-        <v>1.17</v>
+        <v>2.31</v>
       </c>
       <c r="N51" t="n">
-        <v>7.31</v>
+        <v>8.98</v>
       </c>
       <c r="O51" t="n">
         <v>-1.46</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>15.58</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44414</v>
+        <v>44417</v>
       </c>
       <c r="H52" t="n">
-        <v>92.23</v>
+        <v>81.02</v>
       </c>
       <c r="I52" t="n">
         <v>81.51148307909676</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K52" t="n">
-        <v>17.67</v>
+        <v>3.37</v>
       </c>
       <c r="L52" t="n">
         <v>7.57</v>
       </c>
       <c r="M52" t="n">
-        <v>1.52</v>
+        <v>4.46</v>
       </c>
       <c r="N52" t="n">
-        <v>4.21</v>
+        <v>12.15</v>
       </c>
       <c r="O52" t="n">
         <v>8.98</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>21.4</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44435</v>
+        <v>44438</v>
       </c>
       <c r="H53" t="n">
-        <v>83.22</v>
+        <v>86.11</v>
       </c>
       <c r="I53" t="n">
         <v>84.78478419780444</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.72</v>
+        <v>-6.28</v>
       </c>
       <c r="L53" t="n">
         <v>8.76</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>16.79</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44456</v>
+        <v>44459</v>
       </c>
       <c r="H54" t="n">
-        <v>92.18000000000001</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="I54" t="n">
         <v>85.21623012424332</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K54" t="n">
-        <v>7.05</v>
+        <v>-2.5</v>
       </c>
       <c r="L54" t="n">
         <v>3.36</v>
       </c>
       <c r="M54" t="n">
-        <v>0.61</v>
+        <v>3.34</v>
       </c>
       <c r="N54" t="n">
-        <v>2.92</v>
+        <v>8.92</v>
       </c>
       <c r="O54" t="n">
         <v>3.47</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>20.51</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44470</v>
+        <v>44473</v>
       </c>
       <c r="H55" t="n">
-        <v>93.5</v>
+        <v>102.86</v>
       </c>
       <c r="I55" t="n">
         <v>99.13275659154202</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K55" t="n">
-        <v>-11.36</v>
+        <v>-22.51</v>
       </c>
       <c r="L55" t="n">
-        <v>12.12</v>
+        <v>23.62</v>
       </c>
       <c r="M55" t="n">
         <v>1.38</v>
       </c>
       <c r="N55" t="n">
-        <v>6.07</v>
+        <v>10.01</v>
       </c>
       <c r="O55" t="n">
         <v>-8.92</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>19.11</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44496</v>
+        <v>44497</v>
       </c>
       <c r="H56" t="n">
-        <v>99.77</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="I56" t="n">
         <v>98.67259959212504</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K56" t="n">
-        <v>-3</v>
+        <v>-6.19</v>
       </c>
       <c r="L56" t="n">
-        <v>9.279999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="M56" t="n">
-        <v>1.61</v>
+        <v>3.14</v>
       </c>
       <c r="N56" t="n">
         <v>6.29</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>20.4</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44551</v>
+        <v>44552</v>
       </c>
       <c r="H57" t="n">
-        <v>96.39</v>
+        <v>101.04</v>
       </c>
       <c r="I57" t="n">
         <v>100.1067319663171</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K57" t="n">
-        <v>0.1</v>
+        <v>-4.72</v>
       </c>
       <c r="L57" t="n">
         <v>5.94</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>14.71</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H58" t="n">
-        <v>105.99</v>
+        <v>99.09</v>
       </c>
       <c r="I58" t="n">
         <v>100.3103592043303</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K58" t="n">
-        <v>4.9</v>
+        <v>-1.93</v>
       </c>
       <c r="L58" t="n">
         <v>5.86</v>
@@ -3747,7 +4442,7 @@
         <v>1.4</v>
       </c>
       <c r="N58" t="n">
-        <v>3.74</v>
+        <v>6.51</v>
       </c>
       <c r="O58" t="n">
         <v>4.82</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>15.95</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44595</v>
+        <v>44596</v>
       </c>
       <c r="H59" t="n">
-        <v>114.36</v>
+        <v>115.39</v>
       </c>
       <c r="I59" t="n">
         <v>114.8993961940915</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K59" t="n">
-        <v>-15.41</v>
+        <v>-16.45</v>
       </c>
       <c r="L59" t="n">
-        <v>17.19</v>
+        <v>20.05</v>
       </c>
       <c r="M59" t="n">
         <v>1.05</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>10.29</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44610</v>
+        <v>44613</v>
       </c>
       <c r="H60" t="n">
-        <v>112.74</v>
+        <v>109.32</v>
       </c>
       <c r="I60" t="n">
         <v>110.1738364640151</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.3</v>
+        <v>-5.26</v>
       </c>
       <c r="L60" t="n">
-        <v>3.02</v>
+        <v>5.86</v>
       </c>
       <c r="M60" t="n">
         <v>2.04</v>
       </c>
       <c r="N60" t="n">
-        <v>2.82</v>
+        <v>3.03</v>
       </c>
       <c r="O60" t="n">
         <v>0.9</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,25 +4628,25 @@
         <v>14.23</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>44622</v>
+        <v>44623</v>
       </c>
       <c r="H61" t="n">
-        <v>123.32</v>
+        <v>126.3</v>
       </c>
       <c r="I61" t="n">
         <v>124.8731024176546</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K61" t="n">
-        <v>-12.81</v>
+        <v>-15.53</v>
       </c>
       <c r="L61" t="n">
-        <v>15</v>
+        <v>17.24</v>
       </c>
       <c r="M61" t="n">
-        <v>2.54</v>
+        <v>3.21</v>
       </c>
       <c r="N61" t="n">
         <v>4.69</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>14.03</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>44673</v>
+        <v>44676</v>
       </c>
       <c r="H62" t="n">
-        <v>112.74</v>
+        <v>107.07</v>
       </c>
       <c r="I62" t="n">
         <v>112.0351410104018</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K62" t="n">
-        <v>-10.74</v>
+        <v>-15.23</v>
       </c>
       <c r="L62" t="n">
-        <v>12.79</v>
+        <v>15.89</v>
       </c>
       <c r="M62" t="n">
-        <v>2.12</v>
+        <v>2.82</v>
       </c>
       <c r="N62" t="n">
-        <v>4.81</v>
+        <v>5.03</v>
       </c>
       <c r="O62" t="n">
         <v>2.42</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>13.66</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>44771</v>
+        <v>44774</v>
       </c>
       <c r="H63" t="n">
-        <v>76.17</v>
+        <v>77.45</v>
       </c>
       <c r="I63" t="n">
         <v>76.34483497110196</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K63" t="n">
-        <v>28.86</v>
+        <v>27.66</v>
       </c>
       <c r="L63" t="n">
         <v>2.78</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>5</v>
+      </c>
+      <c r="U63" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>10.08</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>44820</v>
+        <v>44823</v>
       </c>
       <c r="H64" t="n">
-        <v>75.44</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="I64" t="n">
         <v>74.15272715406745</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.6</v>
+        <v>-5.94</v>
       </c>
       <c r="L64" t="n">
-        <v>3.99</v>
+        <v>6.33</v>
       </c>
       <c r="M64" t="n">
         <v>3.3</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>12.16</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>44869</v>
+        <v>44872</v>
       </c>
       <c r="H65" t="n">
-        <v>71.81999999999999</v>
+        <v>74.31</v>
       </c>
       <c r="I65" t="n">
         <v>73.94913995559813</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K65" t="n">
-        <v>1.41</v>
+        <v>-2</v>
       </c>
       <c r="L65" t="n">
         <v>4.3</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>10.07</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H66" t="n">
-        <v>74.06999999999999</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="I66" t="n">
         <v>72.62239760756613</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.32</v>
+        <v>-5.33</v>
       </c>
       <c r="L66" t="n">
-        <v>5.07</v>
+        <v>5.79</v>
       </c>
       <c r="M66" t="n">
         <v>1.49</v>
       </c>
       <c r="N66" t="n">
-        <v>2.51</v>
+        <v>5.02</v>
       </c>
       <c r="O66" t="n">
         <v>3.47</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,25 +5042,25 @@
         <v>12.25</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>44924</v>
+        <v>44925</v>
       </c>
       <c r="H67" t="n">
-        <v>77.40000000000001</v>
+        <v>78.72</v>
       </c>
       <c r="I67" t="n">
         <v>78.42526971278713</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K67" t="n">
-        <v>-10.02</v>
+        <v>-11.9</v>
       </c>
       <c r="L67" t="n">
-        <v>10.65</v>
+        <v>14.83</v>
       </c>
       <c r="M67" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="N67" t="n">
         <v>6.48</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>9.48</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>44960</v>
+        <v>44963</v>
       </c>
       <c r="H68" t="n">
-        <v>76.81</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="I68" t="n">
         <v>76.47157457465674</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.43</v>
+        <v>-3.54</v>
       </c>
       <c r="L68" t="n">
-        <v>3.61</v>
+        <v>3.8</v>
       </c>
       <c r="M68" t="n">
         <v>1.53</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>10.42</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>44988</v>
+        <v>44991</v>
       </c>
       <c r="H69" t="n">
-        <v>80.78</v>
+        <v>82.44</v>
       </c>
       <c r="I69" t="n">
         <v>82.26052490851242</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K69" t="n">
-        <v>-6.39</v>
+        <v>-8.57</v>
       </c>
       <c r="L69" t="n">
-        <v>7.41</v>
+        <v>9.15</v>
       </c>
       <c r="M69" t="n">
         <v>0.55</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>9.77</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45009</v>
+        <v>45012</v>
       </c>
       <c r="H70" t="n">
-        <v>75.54000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I70" t="n">
         <v>75.29056292784229</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K70" t="n">
-        <v>-8.369999999999999</v>
+        <v>-8.9</v>
       </c>
       <c r="L70" t="n">
         <v>9.33</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45034</v>
+        <v>45035</v>
       </c>
       <c r="H71" t="n">
-        <v>80.97</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I71" t="n">
         <v>81.76245020031357</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K71" t="n">
-        <v>-7.82</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>8.08</v>
+        <v>10.81</v>
       </c>
       <c r="M71" t="n">
         <v>0.76</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>7.02</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45152</v>
+        <v>45154</v>
       </c>
       <c r="H72" t="n">
-        <v>88.76000000000001</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="I72" t="n">
         <v>88.32107653557857</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K72" t="n">
-        <v>8.050000000000001</v>
+        <v>6.26</v>
       </c>
       <c r="L72" t="n">
         <v>5.6</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>5</v>
+      </c>
+      <c r="U72" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45169</v>
+        <v>45170</v>
       </c>
       <c r="H73" t="n">
-        <v>92.18000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="I73" t="n">
         <v>92.53200396367369</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K73" t="n">
-        <v>-5.6</v>
+        <v>-10.32</v>
       </c>
       <c r="L73" t="n">
-        <v>7.11</v>
+        <v>10.65</v>
       </c>
       <c r="M73" t="n">
         <v>1.28</v>
       </c>
       <c r="N73" t="n">
-        <v>2.54</v>
+        <v>4.47</v>
       </c>
       <c r="O73" t="n">
         <v>-1.66</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>9.32</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45190</v>
+        <v>45191</v>
       </c>
       <c r="H74" t="n">
-        <v>92.09</v>
+        <v>91.55</v>
       </c>
       <c r="I74" t="n">
         <v>91.60898826697428</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K74" t="n">
-        <v>-4.37</v>
+        <v>-4.93</v>
       </c>
       <c r="L74" t="n">
-        <v>4.98</v>
+        <v>5.95</v>
       </c>
       <c r="M74" t="n">
         <v>1.78</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>10.79</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="H75" t="n">
-        <v>94.23999999999999</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="I75" t="n">
         <v>95.41008232930439</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K75" t="n">
-        <v>-2.94</v>
+        <v>-6.15</v>
       </c>
       <c r="L75" t="n">
         <v>9.35</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>4</v>
+      </c>
+      <c r="U75" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H76" t="n">
-        <v>148.48</v>
+        <v>133.31</v>
       </c>
       <c r="I76" t="n">
         <v>142.5752714978149</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K76" t="n">
-        <v>52.79</v>
+        <v>37.18</v>
       </c>
       <c r="L76" t="n">
         <v>3.98</v>
@@ -4773,7 +5684,7 @@
         <v>1.55</v>
       </c>
       <c r="N76" t="n">
-        <v>9.08</v>
+        <v>10.22</v>
       </c>
       <c r="O76" t="n">
         <v>3.12</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>22.84</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="H77" t="n">
-        <v>158.13</v>
+        <v>162.73</v>
       </c>
       <c r="I77" t="n">
         <v>159.8301075461974</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K77" t="n">
-        <v>-18.62</v>
+        <v>-22.07</v>
       </c>
       <c r="L77" t="n">
-        <v>19.13</v>
+        <v>22.44</v>
       </c>
       <c r="M77" t="n">
         <v>1.89</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>15.29</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H78" t="n">
-        <v>192.1</v>
+        <v>155.24</v>
       </c>
       <c r="I78" t="n">
         <v>174.9724881004817</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K78" t="n">
-        <v>18.05</v>
+        <v>-4.6</v>
       </c>
       <c r="L78" t="n">
-        <v>4.63</v>
+        <v>11.46</v>
       </c>
       <c r="M78" t="n">
         <v>1.24</v>
       </c>
       <c r="N78" t="n">
-        <v>4.72</v>
+        <v>19.19</v>
       </c>
       <c r="O78" t="n">
         <v>2.91</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>3</v>
+      </c>
+      <c r="U78" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>31.03</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45548</v>
+        <v>45551</v>
       </c>
       <c r="H79" t="n">
-        <v>178.54</v>
+        <v>185.42</v>
       </c>
       <c r="I79" t="n">
         <v>182.0804217269391</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K79" t="n">
-        <v>-15.01</v>
+        <v>-19.44</v>
       </c>
       <c r="L79" t="n">
         <v>31.82</v>
@@ -4953,7 +5900,19 @@
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>4</v>
+      </c>
+      <c r="U79" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>10.79</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45639</v>
+        <v>45642</v>
       </c>
       <c r="H80" t="n">
-        <v>221.73</v>
+        <v>215.32</v>
       </c>
       <c r="I80" t="n">
         <v>221.5076634614256</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K80" t="n">
-        <v>19.58</v>
+        <v>16.13</v>
       </c>
       <c r="L80" t="n">
         <v>6.92</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>4</v>
+      </c>
+      <c r="U80" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>14.79</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>45786</v>
+        <v>45789</v>
       </c>
       <c r="H81" t="n">
-        <v>156.84</v>
+        <v>168.95</v>
       </c>
       <c r="I81" t="n">
         <v>167.1056583259264</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K81" t="n">
-        <v>27.16</v>
+        <v>21.54</v>
       </c>
       <c r="L81" t="n">
         <v>4.2</v>
@@ -5058,7 +6029,7 @@
         <v>4.22</v>
       </c>
       <c r="N81" t="n">
-        <v>5.73</v>
+        <v>7.72</v>
       </c>
       <c r="O81" t="n">
         <v>-2.89</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>6</v>
+      </c>
+      <c r="U81" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>14.52</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>45868</v>
+        <v>45869</v>
       </c>
       <c r="H82" t="n">
-        <v>187.13</v>
+        <v>185.06</v>
       </c>
       <c r="I82" t="n">
         <v>185.9582409904016</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K82" t="n">
-        <v>10.76</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="L82" t="n">
         <v>4.49</v>
@@ -5124,7 +6107,19 @@
         <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>3</v>
+      </c>
+      <c r="U82" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -5151,28 +6146,28 @@
         <v>7.58</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="H83" t="n">
-        <v>191.79</v>
+        <v>200.53</v>
       </c>
       <c r="I83" t="n">
         <v>196.0326300798199</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K83" t="n">
-        <v>-3.64</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>4.6</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="M83" t="n">
         <v>0.87</v>
       </c>
       <c r="N83" t="n">
-        <v>3.56</v>
+        <v>4.56</v>
       </c>
       <c r="O83" t="n">
         <v>-1.11</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5208,19 +6215,19 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H84" t="n">
-        <v>205.61</v>
+        <v>200.58</v>
       </c>
       <c r="I84" t="n">
         <v>201.3859009503331</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K84" t="n">
-        <v>2.53</v>
+        <v>0.02</v>
       </c>
       <c r="L84" t="n">
         <v>4.82</v>
@@ -5229,7 +6236,7 @@
         <v>1.31</v>
       </c>
       <c r="N84" t="n">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="O84" t="n">
         <v>4.56</v>
@@ -5238,7 +6245,19 @@
         <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S84" t="b">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -5265,22 +6284,22 @@
         <v>9</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="H85" t="n">
-        <v>214.5</v>
+        <v>221.16</v>
       </c>
       <c r="I85" t="n">
         <v>218.6378608977464</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K85" t="n">
-        <v>-6.94</v>
+        <v>-10.26</v>
       </c>
       <c r="L85" t="n">
-        <v>7.68</v>
+        <v>11.98</v>
       </c>
       <c r="M85" t="n">
         <v>0.43</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5322,25 +6353,25 @@
         <v>9.41</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="H86" t="n">
-        <v>385.45</v>
+        <v>354.2</v>
       </c>
       <c r="I86" t="n">
         <v>375.7479013150527</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K86" t="n">
-        <v>74.29000000000001</v>
+        <v>60.16</v>
       </c>
       <c r="L86" t="n">
         <v>3.01</v>
       </c>
       <c r="M86" t="n">
-        <v>3.49</v>
+        <v>8.42</v>
       </c>
       <c r="N86" t="n">
         <v>10.12</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>5</v>
+      </c>
+      <c r="U86" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="87">
@@ -5379,28 +6422,28 @@
         <v>16.87</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="H87" t="n">
-        <v>373.5</v>
+        <v>395.95</v>
       </c>
       <c r="I87" t="n">
         <v>379.4219406351034</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K87" t="n">
-        <v>-5.45</v>
+        <v>-11.79</v>
       </c>
       <c r="L87" t="n">
-        <v>10.66</v>
+        <v>14.14</v>
       </c>
       <c r="M87" t="n">
         <v>5.46</v>
       </c>
       <c r="N87" t="n">
-        <v>4.9</v>
+        <v>6.01</v>
       </c>
       <c r="O87" t="n">
         <v>-8.109999999999999</v>
@@ -5409,7 +6452,19 @@
         <v>1</v>
       </c>
       <c r="Q87" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>2</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -5436,25 +6491,25 @@
         <v>13.4</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="H88" t="n">
-        <v>368.5</v>
+        <v>349.75</v>
       </c>
       <c r="I88" t="n">
         <v>350.1215346729048</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K88" t="n">
-        <v>-6.93</v>
+        <v>-11.67</v>
       </c>
       <c r="L88" t="n">
-        <v>8.94</v>
+        <v>12.36</v>
       </c>
       <c r="M88" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="N88" t="n">
         <v>5.33</v>
@@ -5466,7 +6521,19 @@
         <v>1</v>
       </c>
       <c r="Q88" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S88" t="b">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>1</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -5493,22 +6560,22 @@
         <v>17.2</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="H89" t="n">
-        <v>407.85</v>
+        <v>411.75</v>
       </c>
       <c r="I89" t="n">
         <v>408.4130799548427</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K89" t="n">
-        <v>-16.61</v>
+        <v>-17.73</v>
       </c>
       <c r="L89" t="n">
-        <v>18.88</v>
+        <v>19.33</v>
       </c>
       <c r="M89" t="n">
         <v>2.68</v>
@@ -5523,7 +6590,19 @@
         <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S89" t="b">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>2</v>
+      </c>
+      <c r="U89" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -5550,28 +6629,28 @@
         <v>12.09</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="H90" t="n">
-        <v>433.3</v>
+        <v>399.3</v>
       </c>
       <c r="I90" t="n">
         <v>400.6611942678416</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K90" t="n">
-        <v>5.23</v>
+        <v>-3.02</v>
       </c>
       <c r="L90" t="n">
-        <v>3.58</v>
+        <v>4.25</v>
       </c>
       <c r="M90" t="n">
         <v>1.31</v>
       </c>
       <c r="N90" t="n">
-        <v>2.82</v>
+        <v>7.85</v>
       </c>
       <c r="O90" t="n">
         <v>0.96</v>
@@ -5580,7 +6659,19 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R90" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S90" t="b">
+        <v>1</v>
+      </c>
+      <c r="T90" t="n">
+        <v>2</v>
+      </c>
+      <c r="U90" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -5607,19 +6698,19 @@
         <v>15.34</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="H91" t="n">
-        <v>350.05</v>
+        <v>369</v>
       </c>
       <c r="I91" t="n">
         <v>365.9342439865607</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K91" t="n">
-        <v>12.33</v>
+        <v>7.59</v>
       </c>
       <c r="L91" t="n">
         <v>11.32</v>
@@ -5628,7 +6719,7 @@
         <v>2.54</v>
       </c>
       <c r="N91" t="n">
-        <v>4.62</v>
+        <v>5.41</v>
       </c>
       <c r="O91" t="n">
         <v>-7.85</v>
@@ -5637,7 +6728,19 @@
         <v>1</v>
       </c>
       <c r="Q91" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S91" t="b">
+        <v>1</v>
+      </c>
+      <c r="T91" t="n">
+        <v>4</v>
+      </c>
+      <c r="U91" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="92">
@@ -5664,19 +6767,19 @@
         <v>10.75</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="H92" t="n">
-        <v>381.5</v>
+        <v>372</v>
       </c>
       <c r="I92" t="n">
         <v>373.3082091360699</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K92" t="n">
-        <v>3.39</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L92" t="n">
         <v>4.2</v>
@@ -5694,7 +6797,19 @@
         <v>1</v>
       </c>
       <c r="Q92" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R92" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S92" t="b">
+        <v>1</v>
+      </c>
+      <c r="T92" t="n">
+        <v>2</v>
+      </c>
+      <c r="U92" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -5745,6 +6860,14 @@
       <c r="Q93" t="n">
         <v>39</v>
       </c>
+      <c r="R93" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S93" t="b">
+        <v>1</v>
+      </c>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10703,7 +11826,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44.9</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="6">
@@ -10713,7 +11836,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -10723,7 +11846,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8">
@@ -10733,7 +11856,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -10743,7 +11866,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62.5</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="10">
@@ -10753,7 +11876,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -10763,7 +11886,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -10773,7 +11896,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -10783,7 +11906,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42.9</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="14">
@@ -10793,7 +11916,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.04</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="15">
@@ -10803,7 +11926,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.79</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="16">
@@ -10813,7 +11936,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.8</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="17">
@@ -10823,7 +11946,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>74.29000000000001</v>
+        <v>60.54</v>
       </c>
     </row>
     <row r="18">
@@ -10833,7 +11956,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42.9</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="19">
@@ -10843,7 +11966,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.26</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="20">
@@ -10853,7 +11976,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.92</v>
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -10873,7 +11996,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
@@ -10883,7 +12006,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
@@ -10893,7 +12016,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="25">
@@ -10913,7 +12036,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.54</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="27">
@@ -10923,7 +12046,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.31</v>
+        <v>19.19</v>
       </c>
     </row>
     <row r="28">
@@ -10933,7 +12056,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29">
